--- a/artfynd/A 54057-2022 artfynd.xlsx
+++ b/artfynd/A 54057-2022 artfynd.xlsx
@@ -9112,10 +9112,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112999686</v>
+        <v>113003182</v>
       </c>
       <c r="B77" t="n">
-        <v>89993</v>
+        <v>90029</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9124,41 +9124,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Hundedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>731569</v>
+        <v>731505</v>
       </c>
       <c r="R77" t="n">
-        <v>7059791</v>
+        <v>7059943</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9202,12 +9206,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -9316,10 +9320,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>113003182</v>
+        <v>112999686</v>
       </c>
       <c r="B79" t="n">
-        <v>90029</v>
+        <v>89993</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9328,45 +9332,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Hundedsforsen, Ång</t>
+          <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>731505</v>
+        <v>731569</v>
       </c>
       <c r="R79" t="n">
-        <v>7059943</v>
+        <v>7059791</v>
       </c>
       <c r="S79" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9410,12 +9410,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>

--- a/artfynd/A 54057-2022 artfynd.xlsx
+++ b/artfynd/A 54057-2022 artfynd.xlsx
@@ -9422,10 +9422,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>113015091</v>
+        <v>113015045</v>
       </c>
       <c r="B80" t="n">
-        <v>56681</v>
+        <v>56910</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9438,21 +9438,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100067</v>
+        <v>103021</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9460,31 +9460,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långedsforsen, Långedsforsen, Ång</t>
+          <t>Långedsforsen, Öre älv E4-bron, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>731445</v>
+        <v>731436</v>
       </c>
       <c r="R80" t="n">
-        <v>7059790</v>
+        <v>7059885</v>
       </c>
       <c r="S80" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9540,10 +9536,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>113015045</v>
+        <v>113015091</v>
       </c>
       <c r="B81" t="n">
-        <v>56910</v>
+        <v>56681</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9556,21 +9552,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -9578,27 +9574,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Långedsforsen, Öre älv E4-bron, Ång</t>
+          <t>Långedsforsen, Långedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>731436</v>
+        <v>731445</v>
       </c>
       <c r="R81" t="n">
-        <v>7059885</v>
+        <v>7059790</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>

--- a/artfynd/A 54057-2022 artfynd.xlsx
+++ b/artfynd/A 54057-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54057-2022 artfynd.xlsx
+++ b/artfynd/A 54057-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3012,10 +3012,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104725987</v>
+        <v>104725975</v>
       </c>
       <c r="B22" t="n">
-        <v>77506</v>
+        <v>89392</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3028,21 +3028,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>731450.3399558149</v>
+        <v>731383.1954725545</v>
       </c>
       <c r="R22" t="n">
-        <v>7059744.384500396</v>
+        <v>7059836.856039505</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3124,10 +3124,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104725975</v>
+        <v>104725977</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
+        <v>56395</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3140,34 +3140,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>731383.1954725545</v>
+        <v>731436.4873534199</v>
       </c>
       <c r="R23" t="n">
-        <v>7059836.856039505</v>
+        <v>7059640.181391289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3236,10 +3241,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>104725977</v>
+        <v>104725973</v>
       </c>
       <c r="B24" t="n">
-        <v>56395</v>
+        <v>89392</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3252,39 +3257,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>731436.4873534199</v>
+        <v>731348.3650397587</v>
       </c>
       <c r="R24" t="n">
-        <v>7059640.181391289</v>
+        <v>7059732.016795714</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>104725973</v>
+        <v>104725974</v>
       </c>
       <c r="B25" t="n">
         <v>89392</v>
@@ -3393,10 +3393,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>731348.3650397587</v>
+        <v>731444.8880175345</v>
       </c>
       <c r="R25" t="n">
-        <v>7059732.016795714</v>
+        <v>7059855.660058975</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3465,10 +3465,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>104725974</v>
+        <v>104725995</v>
       </c>
       <c r="B26" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3481,21 +3481,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3505,10 +3505,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>731444.8880175345</v>
+        <v>731512.7539683426</v>
       </c>
       <c r="R26" t="n">
-        <v>7059855.660058975</v>
+        <v>7059710.531467943</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3577,7 +3577,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>104725995</v>
+        <v>104725986</v>
       </c>
       <c r="B27" t="n">
         <v>77506</v>
@@ -3617,10 +3617,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>731512.7539683426</v>
+        <v>731470.1647042678</v>
       </c>
       <c r="R27" t="n">
-        <v>7059710.531467943</v>
+        <v>7059809.712134636</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3689,10 +3689,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>104725986</v>
+        <v>105001081</v>
       </c>
       <c r="B28" t="n">
-        <v>77506</v>
+        <v>89338</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3705,34 +3705,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>112</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>731470.1647042678</v>
+        <v>731406.8906746779</v>
       </c>
       <c r="R28" t="n">
-        <v>7059809.712134636</v>
+        <v>7059684.029516988</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3759,7 +3762,7 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
@@ -3769,7 +3772,7 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-04-07</t>
+          <t>2022-11-26</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
@@ -3783,8 +3786,24 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3794,17 +3813,17 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jon Andersson, Patrik Nygren, kalle Lundin, Roger Olofsson</t>
+          <t>Jon Andersson, Patrik Nygren, Roger Olofsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>105001081</v>
+        <v>105001071</v>
       </c>
       <c r="B29" t="n">
-        <v>89338</v>
+        <v>89392</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3817,37 +3836,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>731406.8906746779</v>
+        <v>731368.474463051</v>
       </c>
       <c r="R29" t="n">
-        <v>7059684.029516988</v>
+        <v>7059799.597976645</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3898,24 +3914,8 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3932,10 +3932,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>105001071</v>
+        <v>105001054</v>
       </c>
       <c r="B30" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3948,21 +3948,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>731368.474463051</v>
+        <v>731556.1736511114</v>
       </c>
       <c r="R30" t="n">
-        <v>7059799.597976645</v>
+        <v>7059905.787151624</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -4044,10 +4044,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>105001054</v>
+        <v>105001085</v>
       </c>
       <c r="B31" t="n">
-        <v>77506</v>
+        <v>5113</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4056,25 +4056,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>731556.1736511114</v>
+        <v>731410.9146302636</v>
       </c>
       <c r="R31" t="n">
-        <v>7059905.787151624</v>
+        <v>7059671.815700579</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -4156,10 +4156,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>105001085</v>
+        <v>105001083</v>
       </c>
       <c r="B32" t="n">
-        <v>5113</v>
+        <v>89356</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4172,21 +4172,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4196,10 +4196,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>731410.9146302636</v>
+        <v>731411.8596614256</v>
       </c>
       <c r="R32" t="n">
-        <v>7059671.815700579</v>
+        <v>7059677.24533963</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4268,10 +4268,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>105001083</v>
+        <v>105001061</v>
       </c>
       <c r="B33" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4280,25 +4280,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4308,10 +4308,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>731411.8596614256</v>
+        <v>731577.1061616455</v>
       </c>
       <c r="R33" t="n">
-        <v>7059677.24533963</v>
+        <v>7059815.300068183</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4380,10 +4380,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>105001061</v>
+        <v>105001094</v>
       </c>
       <c r="B34" t="n">
-        <v>89392</v>
+        <v>56395</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4396,34 +4396,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>731577.1061616455</v>
+        <v>731424.4219610986</v>
       </c>
       <c r="R34" t="n">
-        <v>7059815.300068183</v>
+        <v>7059652.254184282</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4492,10 +4497,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>105001094</v>
+        <v>105001066</v>
       </c>
       <c r="B35" t="n">
-        <v>56395</v>
+        <v>77506</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4508,39 +4513,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>731424.4219610986</v>
+        <v>731425.9401657692</v>
       </c>
       <c r="R35" t="n">
-        <v>7059652.254184282</v>
+        <v>7059778.336803687</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4609,10 +4609,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>105001066</v>
+        <v>105001084</v>
       </c>
       <c r="B36" t="n">
-        <v>77506</v>
+        <v>89356</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4621,25 +4621,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4649,10 +4649,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>731425.9401657692</v>
+        <v>731410.9146302636</v>
       </c>
       <c r="R36" t="n">
-        <v>7059778.336803687</v>
+        <v>7059671.815700579</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4721,10 +4721,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>105001084</v>
+        <v>105001052</v>
       </c>
       <c r="B37" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4733,25 +4733,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4761,10 +4761,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>731410.9146302636</v>
+        <v>731512.5682417073</v>
       </c>
       <c r="R37" t="n">
-        <v>7059671.815700579</v>
+        <v>7059945.479073154</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4833,10 +4833,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>105001052</v>
+        <v>105001075</v>
       </c>
       <c r="B38" t="n">
-        <v>89392</v>
+        <v>89406</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4849,21 +4849,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4873,10 +4873,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>731512.5682417073</v>
+        <v>731330.3540020275</v>
       </c>
       <c r="R38" t="n">
-        <v>7059945.479073154</v>
+        <v>7059745.888491827</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4945,10 +4945,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>105001075</v>
+        <v>105001073</v>
       </c>
       <c r="B39" t="n">
-        <v>89406</v>
+        <v>89410</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4961,21 +4961,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4985,10 +4985,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>731330.3540020275</v>
+        <v>731332.5013712401</v>
       </c>
       <c r="R39" t="n">
-        <v>7059745.888491827</v>
+        <v>7059796.075590911</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5057,10 +5057,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>105001073</v>
+        <v>105001082</v>
       </c>
       <c r="B40" t="n">
-        <v>89410</v>
+        <v>89338</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5073,21 +5073,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>112</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5097,10 +5097,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>731332.5013712401</v>
+        <v>731406.7607560067</v>
       </c>
       <c r="R40" t="n">
-        <v>7059796.075590911</v>
+        <v>7059685.806867215</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5169,10 +5169,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>105001082</v>
+        <v>105001053</v>
       </c>
       <c r="B41" t="n">
-        <v>89338</v>
+        <v>89392</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5185,21 +5185,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>112</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5209,10 +5209,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>731406.7607560067</v>
+        <v>731502.7356293635</v>
       </c>
       <c r="R41" t="n">
-        <v>7059685.806867215</v>
+        <v>7059933.146309381</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5281,10 +5281,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>105001053</v>
+        <v>105001056</v>
       </c>
       <c r="B42" t="n">
-        <v>89392</v>
+        <v>85703</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5297,21 +5297,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5321,10 +5321,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>731502.7356293635</v>
+        <v>731541.3395625666</v>
       </c>
       <c r="R42" t="n">
-        <v>7059933.146309381</v>
+        <v>7059900.681907157</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5393,10 +5393,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>105001056</v>
+        <v>105001067</v>
       </c>
       <c r="B43" t="n">
-        <v>85703</v>
+        <v>89356</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5405,25 +5405,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>510</v>
+        <v>5447</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5433,10 +5433,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>731541.3395625666</v>
+        <v>731425.8102354384</v>
       </c>
       <c r="R43" t="n">
-        <v>7059900.681907157</v>
+        <v>7059780.114101272</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5505,7 +5505,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>105001067</v>
+        <v>105001068</v>
       </c>
       <c r="B44" t="n">
         <v>89356</v>
@@ -5545,10 +5545,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>731425.8102354384</v>
+        <v>731402.5900139628</v>
       </c>
       <c r="R44" t="n">
-        <v>7059780.114101272</v>
+        <v>7059791.817590568</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5617,10 +5617,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>105001068</v>
+        <v>105001060</v>
       </c>
       <c r="B45" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5629,25 +5629,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5657,10 +5657,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>731402.5900139628</v>
+        <v>731628.4335904148</v>
       </c>
       <c r="R45" t="n">
-        <v>7059791.817590568</v>
+        <v>7059816.821818529</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5729,10 +5729,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>105001060</v>
+        <v>105001065</v>
       </c>
       <c r="B46" t="n">
-        <v>89392</v>
+        <v>77506</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5745,21 +5745,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5769,10 +5769,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>731628.4335904148</v>
+        <v>731429.7140902305</v>
       </c>
       <c r="R46" t="n">
-        <v>7059816.821818529</v>
+        <v>7059763.424891178</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5825,6 +5825,21 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5841,10 +5856,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>105001065</v>
+        <v>105001063</v>
       </c>
       <c r="B47" t="n">
-        <v>77506</v>
+        <v>89356</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5853,25 +5868,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5881,10 +5896,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>731429.7140902305</v>
+        <v>731539.4377954181</v>
       </c>
       <c r="R47" t="n">
-        <v>7059763.424891178</v>
+        <v>7059877.761795845</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5937,21 +5952,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5968,7 +5968,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>105001063</v>
+        <v>105001059</v>
       </c>
       <c r="B48" t="n">
         <v>89356</v>
@@ -6008,10 +6008,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>731539.4377954181</v>
+        <v>731611.4675027785</v>
       </c>
       <c r="R48" t="n">
-        <v>7059877.761795845</v>
+        <v>7059871.417245523</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -6080,10 +6080,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>105001059</v>
+        <v>105001090</v>
       </c>
       <c r="B49" t="n">
-        <v>89356</v>
+        <v>89338</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6092,25 +6092,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -6120,10 +6120,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>731611.4675027785</v>
+        <v>731427.2668230262</v>
       </c>
       <c r="R49" t="n">
-        <v>7059871.417245523</v>
+        <v>7059662.2899014</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6192,10 +6192,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>105001090</v>
+        <v>105001070</v>
       </c>
       <c r="B50" t="n">
-        <v>89338</v>
+        <v>89356</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6204,25 +6204,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>112</v>
+        <v>5447</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6232,10 +6232,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>731427.2668230262</v>
+        <v>731366.0810846871</v>
       </c>
       <c r="R50" t="n">
-        <v>7059662.2899014</v>
+        <v>7059826.224630889</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6304,10 +6304,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>105001070</v>
+        <v>105001078</v>
       </c>
       <c r="B51" t="n">
-        <v>89356</v>
+        <v>89392</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6316,25 +6316,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6344,10 +6344,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>731366.0810846871</v>
+        <v>731357.5005101906</v>
       </c>
       <c r="R51" t="n">
-        <v>7059826.224630889</v>
+        <v>7059723.303630172</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6416,10 +6416,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>105001078</v>
+        <v>105001062</v>
       </c>
       <c r="B52" t="n">
-        <v>89392</v>
+        <v>89356</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6428,25 +6428,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6456,10 +6456,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>731357.5005101906</v>
+        <v>731575.0989875239</v>
       </c>
       <c r="R52" t="n">
-        <v>7059723.303630172</v>
+        <v>7059818.280116315</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6528,10 +6528,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>105001062</v>
+        <v>105001069</v>
       </c>
       <c r="B53" t="n">
-        <v>89356</v>
+        <v>89338</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6540,25 +6540,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5447</v>
+        <v>112</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6568,10 +6568,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>731575.0989875239</v>
+        <v>731384.6310269851</v>
       </c>
       <c r="R53" t="n">
-        <v>7059818.280116315</v>
+        <v>7059792.738347441</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6640,10 +6640,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>105001069</v>
+        <v>105001051</v>
       </c>
       <c r="B54" t="n">
-        <v>89338</v>
+        <v>56411</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6656,34 +6656,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>112</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>731384.6310269851</v>
+        <v>731466.2190501932</v>
       </c>
       <c r="R54" t="n">
-        <v>7059792.738347441</v>
+        <v>7059912.608700317</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6736,6 +6741,21 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6752,14 +6772,14 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>105001051</v>
+        <v>105001072</v>
       </c>
       <c r="B55" t="n">
-        <v>56411</v>
+        <v>56311</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -6768,16 +6788,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>100067</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6788,7 +6808,7 @@
       <c r="I55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6797,10 +6817,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>731466.2190501932</v>
+        <v>731329.5817860949</v>
       </c>
       <c r="R55" t="n">
-        <v>7059912.608700317</v>
+        <v>7059793.18207071</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6845,6 +6865,11 @@
           <t>00:00</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>satt längs älven och spanade efter död lax</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6853,21 +6878,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -6884,14 +6894,14 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>105001072</v>
+        <v>112999711</v>
       </c>
       <c r="B56" t="n">
-        <v>56311</v>
+        <v>90047</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
+          <t>Ovaliderad</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -6900,42 +6910,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100067</v>
+        <v>5432</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>731329.5817860949</v>
+        <v>731484</v>
       </c>
       <c r="R56" t="n">
-        <v>7059793.18207071</v>
+        <v>7059928</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6959,27 +6964,17 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2022-11-26</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-28</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>satt längs älven och spanade efter död lax</t>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6994,22 +6989,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jon Andersson, Patrik Nygren, Roger Olofsson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112999711</v>
+        <v>112999692</v>
       </c>
       <c r="B57" t="n">
-        <v>90047</v>
+        <v>56910</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7022,34 +7017,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>731484</v>
+        <v>731636</v>
       </c>
       <c r="R57" t="n">
-        <v>7059928</v>
+        <v>7059752</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7082,11 +7082,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2023-10-28</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7113,10 +7108,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112999692</v>
+        <v>113003184</v>
       </c>
       <c r="B58" t="n">
-        <v>56910</v>
+        <v>90029</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7129,42 +7124,41 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Hundedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>731636</v>
+        <v>731455</v>
       </c>
       <c r="R58" t="n">
-        <v>7059752</v>
+        <v>7059902</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7208,22 +7202,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>113003184</v>
+        <v>112999688</v>
       </c>
       <c r="B59" t="n">
-        <v>90029</v>
+        <v>89993</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7232,45 +7226,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Hundedsforsen, Ång</t>
+          <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>731455</v>
+        <v>731503</v>
       </c>
       <c r="R59" t="n">
-        <v>7059902</v>
+        <v>7059932</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7314,22 +7304,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112999688</v>
+        <v>112999691</v>
       </c>
       <c r="B60" t="n">
-        <v>89993</v>
+        <v>90029</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7338,25 +7328,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7366,10 +7356,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>731503</v>
+        <v>731504</v>
       </c>
       <c r="R60" t="n">
-        <v>7059932</v>
+        <v>7059919</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7428,10 +7418,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112999691</v>
+        <v>113003178</v>
       </c>
       <c r="B61" t="n">
-        <v>90029</v>
+        <v>78105</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7444,37 +7434,41 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Hundedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>731504</v>
+        <v>731528</v>
       </c>
       <c r="R61" t="n">
-        <v>7059919</v>
+        <v>7059888</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7518,22 +7512,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113003178</v>
+        <v>112999685</v>
       </c>
       <c r="B62" t="n">
-        <v>78105</v>
+        <v>89993</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7542,45 +7536,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Hundedsforsen, Ång</t>
+          <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>731528</v>
+        <v>731596</v>
       </c>
       <c r="R62" t="n">
-        <v>7059888</v>
+        <v>7059839</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7610,6 +7600,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7624,22 +7619,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112999685</v>
+        <v>112999714</v>
       </c>
       <c r="B63" t="n">
-        <v>89993</v>
+        <v>91290</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7652,21 +7647,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7676,10 +7671,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>731596</v>
+        <v>731717</v>
       </c>
       <c r="R63" t="n">
-        <v>7059839</v>
+        <v>7059775</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7712,11 +7707,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2023-10-28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7743,10 +7733,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112999714</v>
+        <v>112999684</v>
       </c>
       <c r="B64" t="n">
-        <v>91290</v>
+        <v>89993</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7759,21 +7749,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7783,10 +7773,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>731717</v>
+        <v>731608</v>
       </c>
       <c r="R64" t="n">
-        <v>7059775</v>
+        <v>7059806</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7819,6 +7809,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7845,10 +7840,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112999684</v>
+        <v>112999713</v>
       </c>
       <c r="B65" t="n">
-        <v>89993</v>
+        <v>91290</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7861,21 +7856,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7885,10 +7880,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>731608</v>
+        <v>731678</v>
       </c>
       <c r="R65" t="n">
-        <v>7059806</v>
+        <v>7059720</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7921,11 +7916,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2023-10-28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>granlåga</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7952,10 +7942,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112999713</v>
+        <v>113003175</v>
       </c>
       <c r="B66" t="n">
-        <v>91290</v>
+        <v>91333</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7964,41 +7954,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Hundedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>731678</v>
+        <v>731677</v>
       </c>
       <c r="R66" t="n">
-        <v>7059720</v>
+        <v>7059744</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8042,22 +8036,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>113003175</v>
+        <v>113003187</v>
       </c>
       <c r="B67" t="n">
-        <v>91333</v>
+        <v>89975</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8070,21 +8064,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5448</v>
+        <v>112</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -8098,10 +8092,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>731677</v>
+        <v>731404</v>
       </c>
       <c r="R67" t="n">
-        <v>7059744</v>
+        <v>7059864</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8160,10 +8154,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>113003187</v>
+        <v>113003176</v>
       </c>
       <c r="B68" t="n">
-        <v>89975</v>
+        <v>91290</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8172,25 +8166,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>112</v>
+        <v>4364</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -8204,10 +8198,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>731404</v>
+        <v>731664</v>
       </c>
       <c r="R68" t="n">
-        <v>7059864</v>
+        <v>7059743</v>
       </c>
       <c r="S68" t="n">
         <v>5</v>
@@ -8266,10 +8260,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>113003176</v>
+        <v>112999693</v>
       </c>
       <c r="B69" t="n">
-        <v>91290</v>
+        <v>56910</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8278,45 +8272,46 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Hundedsforsen, Ång</t>
+          <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>731664</v>
+        <v>731668</v>
       </c>
       <c r="R69" t="n">
-        <v>7059743</v>
+        <v>7059977</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8360,22 +8355,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112999693</v>
+        <v>112999689</v>
       </c>
       <c r="B70" t="n">
-        <v>56910</v>
+        <v>90029</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8388,39 +8383,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>731668</v>
+        <v>731497</v>
       </c>
       <c r="R70" t="n">
-        <v>7059977</v>
+        <v>7059940</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8453,6 +8443,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2023-10-28</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>granlåga och stubbe</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8479,10 +8474,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112999689</v>
+        <v>113003180</v>
       </c>
       <c r="B71" t="n">
-        <v>90029</v>
+        <v>78105</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8495,37 +8490,41 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Hundedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>731497</v>
+        <v>731531</v>
       </c>
       <c r="R71" t="n">
-        <v>7059940</v>
+        <v>7059894</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8555,11 +8554,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2023-10-28</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>granlåga och stubbe</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8574,22 +8568,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>113003180</v>
+        <v>113003181</v>
       </c>
       <c r="B72" t="n">
-        <v>78105</v>
+        <v>90029</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8602,21 +8596,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -8630,10 +8624,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>731531</v>
+        <v>731509</v>
       </c>
       <c r="R72" t="n">
-        <v>7059894</v>
+        <v>7059926</v>
       </c>
       <c r="S72" t="n">
         <v>5</v>
@@ -8692,7 +8686,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>113003181</v>
+        <v>112999690</v>
       </c>
       <c r="B73" t="n">
         <v>90029</v>
@@ -8725,24 +8719,20 @@
           <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Hundedsforsen, Ång</t>
+          <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>731509</v>
+        <v>731617</v>
       </c>
       <c r="R73" t="n">
-        <v>7059926</v>
+        <v>7059815</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8786,22 +8776,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112999690</v>
+        <v>113003173</v>
       </c>
       <c r="B74" t="n">
-        <v>90029</v>
+        <v>89993</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8810,41 +8800,45 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Hundedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>731617</v>
+        <v>731551</v>
       </c>
       <c r="R74" t="n">
-        <v>7059815</v>
+        <v>7059720</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8888,22 +8882,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>113003173</v>
+        <v>113003177</v>
       </c>
       <c r="B75" t="n">
-        <v>89993</v>
+        <v>78105</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8912,25 +8906,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -8944,10 +8938,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>731551</v>
+        <v>731537</v>
       </c>
       <c r="R75" t="n">
-        <v>7059720</v>
+        <v>7059840</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -9006,10 +9000,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>113003177</v>
+        <v>113003182</v>
       </c>
       <c r="B76" t="n">
-        <v>78105</v>
+        <v>90029</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9022,21 +9016,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -9050,10 +9044,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>731537</v>
+        <v>731505</v>
       </c>
       <c r="R76" t="n">
-        <v>7059840</v>
+        <v>7059943</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -9112,10 +9106,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>113003182</v>
+        <v>112999687</v>
       </c>
       <c r="B77" t="n">
-        <v>90029</v>
+        <v>89993</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9124,45 +9118,41 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Hundedsforsen, Ång</t>
+          <t>E4:ans bro över Öreälven, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>731505</v>
+        <v>731617</v>
       </c>
       <c r="R77" t="n">
-        <v>7059943</v>
+        <v>7059853</v>
       </c>
       <c r="S77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9206,19 +9196,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Jon Andersson</t>
+          <t>Roger Olofsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112999687</v>
+        <v>112999686</v>
       </c>
       <c r="B78" t="n">
         <v>89993</v>
@@ -9258,10 +9248,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>731617</v>
+        <v>731569</v>
       </c>
       <c r="R78" t="n">
-        <v>7059853</v>
+        <v>7059791</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9320,10 +9310,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112999686</v>
+        <v>113015045</v>
       </c>
       <c r="B79" t="n">
-        <v>89993</v>
+        <v>56910</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9332,38 +9322,50 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5447</v>
+        <v>103021</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>E4:ans bro över Öreälven, Ång</t>
+          <t>Långedsforsen, Öre älv E4-bron, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>731569</v>
+        <v>731436</v>
       </c>
       <c r="R79" t="n">
-        <v>7059791</v>
+        <v>7059885</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9390,12 +9392,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2023-10-28</t>
+          <t>2023-10-31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9410,26 +9412,26 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Roger Olofsson</t>
+          <t>Jon Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>113015045</v>
+        <v>113015091</v>
       </c>
       <c r="B80" t="n">
-        <v>56910</v>
+        <v>57181</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Godkänd baserat på observatörens uppgifter</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -9438,21 +9440,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>103021</v>
+        <v>100067</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -9460,27 +9462,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>2K+</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Långedsforsen, Öre älv E4-bron, Ång</t>
+          <t>Långedsforsen, Långedsforsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>731436</v>
+        <v>731445</v>
       </c>
       <c r="R80" t="n">
-        <v>7059885</v>
+        <v>7059790</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9533,124 +9539,6 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>113015091</v>
-      </c>
-      <c r="B81" t="n">
-        <v>57181</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E81" t="n">
-        <v>100067</v>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>Havsörn</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Haliaeetus albicilla</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>2K+</t>
-        </is>
-      </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>Långedsforsen, Långedsforsen, Ång</t>
-        </is>
-      </c>
-      <c r="Q81" t="n">
-        <v>731445</v>
-      </c>
-      <c r="R81" t="n">
-        <v>7059790</v>
-      </c>
-      <c r="S81" t="n">
-        <v>50</v>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U81" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="V81" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
-        <is>
-          <t>Nordmaling</t>
-        </is>
-      </c>
-      <c r="Y81" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="AA81" t="inlineStr">
-        <is>
-          <t>2023-10-31</t>
-        </is>
-      </c>
-      <c r="AD81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG81" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT81" t="inlineStr"/>
-      <c r="AW81" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr">
-        <is>
-          <t>Jon Andersson</t>
-        </is>
-      </c>
-      <c r="AY81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
